--- a/data/trans_orig/Q4502_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q4502_R-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron camiseta para protegerse del sol el pasado verano al aire libre en 2007</t>
+          <t>Población según la frecuencia con la que utilizaron camiseta para protegerse del sol el pasado verano al aire libre en 2007 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87126</t>
+          <t>86770</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>124872</t>
+          <t>125623</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35966</t>
+          <t>36241</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63530</t>
+          <t>62297</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129741</t>
+          <t>132938</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>176564</t>
+          <t>177024</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96392</t>
+          <t>97711</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133505</t>
+          <t>133314</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47027</t>
+          <t>49210</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76774</t>
+          <t>77315</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>153013</t>
+          <t>153788</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>199088</t>
+          <t>199643</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>126155</t>
+          <t>127462</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>167500</t>
+          <t>166877</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>91192</t>
+          <t>90709</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>123862</t>
+          <t>123646</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>229594</t>
+          <t>229933</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>283376</t>
+          <t>282170</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19286</t>
+          <t>19312</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40427</t>
+          <t>42004</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26707</t>
+          <t>26192</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49790</t>
+          <t>48818</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51431</t>
+          <t>50253</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83371</t>
+          <t>82046</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63721</t>
+          <t>64445</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96489</t>
+          <t>96374</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39538</t>
+          <t>39533</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65155</t>
+          <t>65599</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109831</t>
+          <t>109920</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>152103</t>
+          <t>153830</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52441</t>
+          <t>53667</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83535</t>
+          <t>85236</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51943</t>
+          <t>50651</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81000</t>
+          <t>82562</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113518</t>
+          <t>113211</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157312</t>
+          <t>157193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69029</t>
+          <t>69685</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101148</t>
+          <t>102848</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45542</t>
+          <t>45223</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73022</t>
+          <t>73971</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121066</t>
+          <t>122889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>163673</t>
+          <t>164483</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92548</t>
+          <t>92834</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>127316</t>
+          <t>126740</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>96105</t>
+          <t>94499</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>130160</t>
+          <t>131800</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>199017</t>
+          <t>197578</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>247674</t>
+          <t>247565</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13169</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32306</t>
+          <t>32047</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28451</t>
+          <t>28222</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50704</t>
+          <t>51487</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47240</t>
+          <t>47500</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76766</t>
+          <t>78253</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68633</t>
+          <t>66641</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100859</t>
+          <t>101469</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80888</t>
+          <t>79594</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>112176</t>
+          <t>111728</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155755</t>
+          <t>155605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>202571</t>
+          <t>204189</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95391</t>
+          <t>93995</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>131693</t>
+          <t>133368</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25890</t>
+          <t>26132</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47208</t>
+          <t>47231</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128662</t>
+          <t>128538</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172233</t>
+          <t>172818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112576</t>
+          <t>113358</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152853</t>
+          <t>152210</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26816</t>
+          <t>26807</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47962</t>
+          <t>50096</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>145335</t>
+          <t>143643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>191831</t>
+          <t>188486</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>128655</t>
+          <t>129771</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>170227</t>
+          <t>171234</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39516</t>
+          <t>39714</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63383</t>
+          <t>64245</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>177698</t>
+          <t>177845</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>224867</t>
+          <t>226593</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31393</t>
+          <t>31446</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58991</t>
+          <t>56857</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>15898</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37886</t>
+          <t>37151</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66007</t>
+          <t>65289</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>89985</t>
+          <t>88680</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127853</t>
+          <t>126415</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24678</t>
+          <t>25033</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45184</t>
+          <t>45637</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122238</t>
+          <t>121166</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165479</t>
+          <t>165087</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>281954</t>
+          <t>278640</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>342201</t>
+          <t>338757</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>129857</t>
+          <t>125820</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>173204</t>
+          <t>168727</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>419988</t>
+          <t>422333</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>493139</t>
+          <t>496972</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>265939</t>
+          <t>263934</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>324980</t>
+          <t>322237</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>125660</t>
+          <t>123012</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>167389</t>
+          <t>166436</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>400071</t>
+          <t>401466</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>477052</t>
+          <t>475710</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>314025</t>
+          <t>321059</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>378487</t>
+          <t>382807</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>175187</t>
+          <t>172657</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>222853</t>
+          <t>219011</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>509261</t>
+          <t>506386</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>586545</t>
+          <t>586532</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47200</t>
+          <t>48089</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78313</t>
+          <t>78700</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44891</t>
+          <t>44637</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73131</t>
+          <t>73702</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>100754</t>
+          <t>99765</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>142481</t>
+          <t>140109</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>197526</t>
+          <t>196973</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>251999</t>
+          <t>248992</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>145340</t>
+          <t>147693</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>187793</t>
+          <t>190508</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>355518</t>
+          <t>353672</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>429489</t>
+          <t>424818</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>73787</t>
+          <t>71598</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>107899</t>
+          <t>106031</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>93072</t>
+          <t>93150</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>129985</t>
+          <t>130911</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>178221</t>
+          <t>176873</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>228924</t>
+          <t>227785</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>48598</t>
+          <t>47963</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>76170</t>
+          <t>75694</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>84710</t>
+          <t>83823</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>121404</t>
+          <t>120630</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>139531</t>
+          <t>140243</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>188351</t>
+          <t>188310</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>86259</t>
+          <t>86595</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>120957</t>
+          <t>120892</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>139773</t>
+          <t>140504</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>183278</t>
+          <t>183876</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>235647</t>
+          <t>240736</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>292944</t>
+          <t>297397</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10096</t>
+          <t>9729</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>25885</t>
+          <t>27440</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>29847</t>
+          <t>30195</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>54774</t>
+          <t>54766</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>44338</t>
+          <t>46086</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>72459</t>
+          <t>74305</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>64295</t>
+          <t>64638</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>95496</t>
+          <t>95761</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>131561</t>
+          <t>132621</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>173260</t>
+          <t>175348</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>205806</t>
+          <t>205567</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>257619</t>
+          <t>255056</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>24317</t>
+          <t>24776</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>45960</t>
+          <t>46117</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>242416</t>
+          <t>244233</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>297571</t>
+          <t>302396</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>274234</t>
+          <t>274113</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>339712</t>
+          <t>336968</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>50338</t>
+          <t>53282</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>79420</t>
+          <t>80895</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>186215</t>
+          <t>184181</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>238419</t>
+          <t>237658</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>247217</t>
+          <t>245361</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>306660</t>
+          <t>304879</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>90920</t>
+          <t>91199</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>124210</t>
+          <t>123459</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>331782</t>
+          <t>330916</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>392653</t>
+          <t>393587</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>430642</t>
+          <t>433481</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>503398</t>
+          <t>506153</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>16276</t>
+          <t>16768</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>35463</t>
+          <t>36152</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>57338</t>
+          <t>57566</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>89811</t>
+          <t>90448</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>81026</t>
+          <t>81048</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>119479</t>
+          <t>117212</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>53679</t>
+          <t>53010</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>82140</t>
+          <t>83642</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>302851</t>
+          <t>299493</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>364535</t>
+          <t>362434</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>366490</t>
+          <t>365694</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>435729</t>
+          <t>433056</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>673844</t>
+          <t>671356</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>767632</t>
+          <t>765749</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>635185</t>
+          <t>636057</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>725581</t>
+          <t>729572</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1333148</t>
+          <t>1324550</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1467481</t>
+          <t>1460838</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>704006</t>
+          <t>702449</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>800150</t>
+          <t>799019</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>568953</t>
+          <t>569083</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>659390</t>
+          <t>658274</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1299020</t>
+          <t>1292658</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1432445</t>
+          <t>1425461</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>909878</t>
+          <t>916041</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1014717</t>
+          <t>1025427</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>939611</t>
+          <t>937575</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1045889</t>
+          <t>1041900</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1882502</t>
+          <t>1890107</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2028101</t>
+          <t>2032780</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>170443</t>
+          <t>169145</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>222916</t>
+          <t>221480</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>228191</t>
+          <t>225738</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>292186</t>
+          <t>287536</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>415073</t>
+          <t>413355</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>498465</t>
+          <t>492525</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>594596</t>
+          <t>595479</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>691734</t>
+          <t>687005</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>784825</t>
+          <t>783586</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>886083</t>
+          <t>884761</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1407064</t>
+          <t>1401220</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1539893</t>
+          <t>1534528</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron camiseta para protegerse del sol el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron camiseta para protegerse del sol el pasado verano al aire libre en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>139153</t>
+          <t>138665</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>180450</t>
+          <t>180865</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92573</t>
+          <t>93050</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>128843</t>
+          <t>128504</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>243988</t>
+          <t>240200</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>295792</t>
+          <t>297851</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88902</t>
+          <t>88597</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125674</t>
+          <t>125472</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50587</t>
+          <t>48811</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80082</t>
+          <t>81932</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>146382</t>
+          <t>146606</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>195729</t>
+          <t>197180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65243</t>
+          <t>64612</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99992</t>
+          <t>98380</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46854</t>
+          <t>46751</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>77157</t>
+          <t>77090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>117562</t>
+          <t>118951</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>164670</t>
+          <t>164585</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18846</t>
+          <t>18381</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40865</t>
+          <t>41094</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16703</t>
+          <t>16635</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36961</t>
+          <t>36117</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40298</t>
+          <t>41898</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69102</t>
+          <t>69086</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47468</t>
+          <t>48383</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78114</t>
+          <t>78393</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38138</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64895</t>
+          <t>64912</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93181</t>
+          <t>91647</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>132593</t>
+          <t>134682</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144120</t>
+          <t>144761</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>188551</t>
+          <t>187631</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86825</t>
+          <t>83900</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121271</t>
+          <t>120178</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>242275</t>
+          <t>241708</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>296937</t>
+          <t>298111</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86622</t>
+          <t>85470</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>124640</t>
+          <t>124002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49002</t>
+          <t>50542</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79535</t>
+          <t>79350</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>143716</t>
+          <t>140361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194123</t>
+          <t>191253</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63416</t>
+          <t>64117</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>96909</t>
+          <t>99630</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53232</t>
+          <t>52555</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83896</t>
+          <t>83897</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>124262</t>
+          <t>124585</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>170198</t>
+          <t>171955</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18305</t>
+          <t>19154</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>20429</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43727</t>
+          <t>43335</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>28354</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55017</t>
+          <t>56327</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44120</t>
+          <t>43212</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73551</t>
+          <t>74277</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58951</t>
+          <t>59524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91586</t>
+          <t>92580</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111175</t>
+          <t>111825</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>154334</t>
+          <t>155410</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>231390</t>
+          <t>230947</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>282602</t>
+          <t>281199</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86366</t>
+          <t>85122</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>117076</t>
+          <t>118692</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>327817</t>
+          <t>331387</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>387786</t>
+          <t>390634</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,01%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110338</t>
+          <t>111368</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>153655</t>
+          <t>150542</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29432</t>
+          <t>30265</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54200</t>
+          <t>54958</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>148397</t>
+          <t>148939</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>197717</t>
+          <t>196759</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88837</t>
+          <t>89861</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>128011</t>
+          <t>129060</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34552</t>
+          <t>34870</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>59351</t>
+          <t>60188</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>133606</t>
+          <t>133218</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>179108</t>
+          <t>178153</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15288</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36388</t>
+          <t>37185</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10192</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27684</t>
+          <t>27706</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30654</t>
+          <t>29236</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57211</t>
+          <t>55038</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>86991</t>
+          <t>90151</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127845</t>
+          <t>127968</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40816</t>
+          <t>42074</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66774</t>
+          <t>69752</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>138968</t>
+          <t>136928</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>185671</t>
+          <t>185912</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>446983</t>
+          <t>448296</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>516995</t>
+          <t>516129</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>250683</t>
+          <t>252012</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>304626</t>
+          <t>306797</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>713040</t>
+          <t>716274</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>803370</t>
+          <t>800124</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,59%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>216642</t>
+          <t>216676</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>273858</t>
+          <t>275452</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127371</t>
+          <t>124978</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>171907</t>
+          <t>168699</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>355044</t>
+          <t>354330</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>429203</t>
+          <t>428546</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>152520</t>
+          <t>152617</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>202583</t>
+          <t>202339</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>113807</t>
+          <t>110349</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>158768</t>
+          <t>156072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>279239</t>
+          <t>277780</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>343712</t>
+          <t>344562</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38223</t>
+          <t>39018</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>67898</t>
+          <t>68947</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35231</t>
+          <t>35054</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62810</t>
+          <t>62140</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>79337</t>
+          <t>81039</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>120436</t>
+          <t>119809</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>180605</t>
+          <t>176627</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>234301</t>
+          <t>232554</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>137297</t>
+          <t>137019</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>182973</t>
+          <t>184360</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>327978</t>
+          <t>331195</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>400369</t>
+          <t>402584</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>191920</t>
+          <t>193628</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>235819</t>
+          <t>238409</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>250047</t>
+          <t>248092</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>306140</t>
+          <t>303935</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>451400</t>
+          <t>451536</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>523672</t>
+          <t>525716</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>72118</t>
+          <t>71831</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>108869</t>
+          <t>108214</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>111966</t>
+          <t>111817</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>152441</t>
+          <t>154083</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>193562</t>
+          <t>197268</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>249288</t>
+          <t>249483</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>64238</t>
+          <t>64320</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>99202</t>
+          <t>97930</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>89590</t>
+          <t>89089</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>130139</t>
+          <t>128366</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>162803</t>
+          <t>165401</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>216737</t>
+          <t>216308</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>10701</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>28547</t>
+          <t>27923</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>35275</t>
+          <t>34531</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>64624</t>
+          <t>62555</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>50430</t>
+          <t>50522</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>82574</t>
+          <t>83991</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>90230</t>
+          <t>89494</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>127317</t>
+          <t>126937</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>173509</t>
+          <t>170541</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>220502</t>
+          <t>220666</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>275532</t>
+          <t>272643</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>337223</t>
+          <t>334726</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>60509</t>
+          <t>60393</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>89961</t>
+          <t>90477</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>473394</t>
+          <t>472186</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>538988</t>
+          <t>539563</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>544148</t>
+          <t>542376</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>616029</t>
+          <t>616174</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,84%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>52544</t>
+          <t>52026</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>80130</t>
+          <t>79966</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>167437</t>
+          <t>167697</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>219070</t>
+          <t>217240</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>230437</t>
+          <t>231087</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>287747</t>
+          <t>290311</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>48986</t>
+          <t>48211</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>76236</t>
+          <t>75897</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,82 +9391,82 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
+          <t>18,06%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>28,44%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>162305</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>138747</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>187957</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>14,66%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>12,53%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>16,98%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>224406</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>197294</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>252200</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>16,33%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>14,36%</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
           <t>18,35%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>28,57%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>162305</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>140663</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>185822</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>14,66%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>12,71%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>16,78%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>224406</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>196957</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>253480</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>16,33%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>14,33%</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>13973</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>31435</t>
+          <t>30951</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>45717</t>
+          <t>45167</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>76497</t>
+          <t>76959</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>64002</t>
+          <t>65328</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>100534</t>
+          <t>98402</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>33680</t>
+          <t>34038</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>58940</t>
+          <t>58218</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>161780</t>
+          <t>164822</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>212182</t>
+          <t>214100</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>202781</t>
+          <t>204658</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>261357</t>
+          <t>262118</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1295228</t>
+          <t>1295596</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1417555</t>
+          <t>1413568</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1316325</t>
+          <t>1323585</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1436545</t>
+          <t>1439552</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2650069</t>
+          <t>2635289</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2812355</t>
+          <t>2805073</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,31%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>688335</t>
+          <t>689233</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>789786</t>
+          <t>785200</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>591723</t>
+          <t>596079</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>685013</t>
+          <t>688320</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1317015</t>
+          <t>1311268</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1445693</t>
+          <t>1445791</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>543131</t>
+          <t>543058</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>636152</t>
+          <t>635113</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>530795</t>
+          <t>529814</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>622286</t>
+          <t>617661</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1097648</t>
+          <t>1104291</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1229129</t>
+          <t>1233359</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>133458</t>
+          <t>130666</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>179744</t>
+          <t>178367</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>196199</t>
+          <t>199055</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>259539</t>
+          <t>260501</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>341179</t>
+          <t>341999</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>421931</t>
+          <t>420927</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>541024</t>
+          <t>541793</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>634695</t>
+          <t>631239</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>675876</t>
+          <t>671587</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>775517</t>
+          <t>775712</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1240231</t>
+          <t>1245534</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1376037</t>
+          <t>1386471</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron camiseta para protegerse del sol el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron camiseta para protegerse del sol el pasado verano al aire libre en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82622</t>
+          <t>79922</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>118009</t>
+          <t>117317</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63102</t>
+          <t>61230</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94638</t>
+          <t>93285</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>153052</t>
+          <t>152716</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>200209</t>
+          <t>201019</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>133463</t>
+          <t>133839</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>174674</t>
+          <t>175395</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83762</t>
+          <t>83636</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>117719</t>
+          <t>114925</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>228391</t>
+          <t>226501</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>279535</t>
+          <t>280601</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74815</t>
+          <t>75739</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112469</t>
+          <t>110154</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68198</t>
+          <t>69132</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>100572</t>
+          <t>99381</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>152474</t>
+          <t>152108</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>200288</t>
+          <t>200834</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38286</t>
+          <t>38072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15684</t>
+          <t>14993</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36031</t>
+          <t>34190</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36693</t>
+          <t>35885</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64906</t>
+          <t>64502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43769</t>
+          <t>43820</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74008</t>
+          <t>73028</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50487</t>
+          <t>48214</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79411</t>
+          <t>78498</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102036</t>
+          <t>101581</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141311</t>
+          <t>145356</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72814</t>
+          <t>73940</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>108853</t>
+          <t>107265</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55759</t>
+          <t>54336</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87854</t>
+          <t>86770</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138083</t>
+          <t>137639</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>183976</t>
+          <t>186043</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105362</t>
+          <t>106654</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>144028</t>
+          <t>144930</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111362</t>
+          <t>111346</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147745</t>
+          <t>149093</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>227381</t>
+          <t>226989</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>281387</t>
+          <t>279741</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74473</t>
+          <t>76727</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109954</t>
+          <t>110762</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>69160</t>
+          <t>67003</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>101679</t>
+          <t>101444</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>156271</t>
+          <t>155740</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>201919</t>
+          <t>202414</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30553</t>
+          <t>30406</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13540</t>
+          <t>13628</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32056</t>
+          <t>33047</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29185</t>
+          <t>30137</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54988</t>
+          <t>55664</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34376</t>
+          <t>33232</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61104</t>
+          <t>61971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48149</t>
+          <t>48878</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79179</t>
+          <t>79155</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,7 +11932,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92822</t>
+          <t>92005</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>133366</t>
+          <t>129723</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110602</t>
+          <t>109996</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>151400</t>
+          <t>150540</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31412</t>
+          <t>32008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54496</t>
+          <t>56172</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>149646</t>
+          <t>152331</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>198626</t>
+          <t>196873</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>137297</t>
+          <t>138725</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>179906</t>
+          <t>182375</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39299</t>
+          <t>40005</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63588</t>
+          <t>63150</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>184867</t>
+          <t>184868</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>234461</t>
+          <t>233504</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>104641</t>
+          <t>106457</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>145517</t>
+          <t>146582</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22289</t>
+          <t>21504</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41241</t>
+          <t>40430</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>135373</t>
+          <t>133834</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>180564</t>
+          <t>178966</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>22396</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44039</t>
+          <t>44705</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22348</t>
+          <t>22295</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32322</t>
+          <t>34147</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59959</t>
+          <t>60471</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58726</t>
+          <t>58696</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91095</t>
+          <t>92317</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19526</t>
+          <t>19188</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39335</t>
+          <t>39837</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86183</t>
+          <t>85153</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>123576</t>
+          <t>122851</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>251120</t>
+          <t>246223</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>308792</t>
+          <t>306557</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>172286</t>
+          <t>173023</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>223014</t>
+          <t>223800</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>440903</t>
+          <t>440443</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>513363</t>
+          <t>515316</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>340785</t>
+          <t>338613</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>402870</t>
+          <t>401636</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>214987</t>
+          <t>210465</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>268766</t>
+          <t>265664</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>570828</t>
+          <t>569997</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>660223</t>
+          <t>655350</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>213296</t>
+          <t>216181</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>268943</t>
+          <t>269815</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>157240</t>
+          <t>159599</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>206866</t>
+          <t>206872</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>390508</t>
+          <t>381404</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>463873</t>
+          <t>457251</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50627</t>
+          <t>50488</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>83434</t>
+          <t>84046</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36757</t>
+          <t>35907</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62667</t>
+          <t>63525</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>95108</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>139034</t>
+          <t>137595</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>161462</t>
+          <t>163543</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>214027</t>
+          <t>214286</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>131180</t>
+          <t>131683</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>174969</t>
+          <t>178452</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>302543</t>
+          <t>303619</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>374718</t>
+          <t>372661</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>139921</t>
+          <t>140368</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>183513</t>
+          <t>183890</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>179090</t>
+          <t>183331</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>230471</t>
+          <t>228733</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>330830</t>
+          <t>333204</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>399236</t>
+          <t>400251</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>177291</t>
+          <t>174136</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>221320</t>
+          <t>219751</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>204816</t>
+          <t>201715</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>254012</t>
+          <t>253071</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>392222</t>
+          <t>396567</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>461036</t>
+          <t>461539</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,99%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>124959</t>
+          <t>125446</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>166536</t>
+          <t>164530</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>113231</t>
+          <t>115925</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>156931</t>
+          <t>156971</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>252373</t>
+          <t>249927</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>311872</t>
+          <t>312519</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19314</t>
+          <t>19167</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41025</t>
+          <t>40561</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24498</t>
+          <t>24475</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>46630</t>
+          <t>48283</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>49128</t>
+          <t>48731</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>81714</t>
+          <t>79118</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>72052</t>
+          <t>71834</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>105976</t>
+          <t>106882</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>112700</t>
+          <t>113456</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>155830</t>
+          <t>157377</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>196580</t>
+          <t>196270</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>252851</t>
+          <t>251348</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>54650</t>
+          <t>55282</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>83820</t>
+          <t>83748</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>216812</t>
+          <t>215168</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>276872</t>
+          <t>273808</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>280736</t>
+          <t>280887</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>343428</t>
+          <t>346122</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>74291</t>
+          <t>75522</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>106333</t>
+          <t>106682</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,47 +14286,47 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
+          <t>26,5%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>37,44%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>312055</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>280806</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>344384</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>28,97%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
           <t>26,07%</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>312055</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>283955</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>345595</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>28,97%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>26,36%</t>
-        </is>
-      </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>367411</t>
+          <t>366722</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>437133</t>
+          <t>437124</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,7 +14356,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>59352</t>
+          <t>59791</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>91386</t>
+          <t>90273</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>156846</t>
+          <t>156325</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>208070</t>
+          <t>205421</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>227396</t>
+          <t>226541</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>288456</t>
+          <t>287813</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>22925</t>
+          <t>23693</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>65320</t>
+          <t>64631</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>100946</t>
+          <t>102116</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>76716</t>
+          <t>79521</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>116562</t>
+          <t>118030</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>27437</t>
+          <t>26783</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>49721</t>
+          <t>50553</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>230004</t>
+          <t>224888</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>288345</t>
+          <t>285451</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>264242</t>
+          <t>262858</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>327055</t>
+          <t>324975</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>772258</t>
+          <t>777457</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>876713</t>
+          <t>881102</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>786301</t>
+          <t>788596</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>896164</t>
+          <t>887608</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1598132</t>
+          <t>1589890</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1734019</t>
+          <t>1734376</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1041536</t>
+          <t>1039944</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1152410</t>
+          <t>1153569</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1004273</t>
+          <t>1003241</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1114219</t>
+          <t>1116841</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2077654</t>
+          <t>2076422</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2225780</t>
+          <t>2234064</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>722048</t>
+          <t>720423</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>818248</t>
+          <t>819388</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>651638</t>
+          <t>653236</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>748383</t>
+          <t>747264</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1402164</t>
+          <t>1404579</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1541669</t>
+          <t>1536987</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>163225</t>
+          <t>160481</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>214944</t>
+          <t>215280</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>197333</t>
+          <t>199846</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>254761</t>
+          <t>253816</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>375316</t>
+          <t>372014</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>456234</t>
+          <t>455577</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>449786</t>
+          <t>448291</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>531387</t>
+          <t>535143</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>651646</t>
+          <t>647864</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>752119</t>
+          <t>745338</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1131815</t>
+          <t>1125806</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1252712</t>
+          <t>1258133</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4502_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q4502_R-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>86770</t>
+          <t>86568</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125623</t>
+          <t>124129</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36241</t>
+          <t>36511</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62297</t>
+          <t>60939</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>132938</t>
+          <t>131183</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>177024</t>
+          <t>178136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97711</t>
+          <t>94768</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133314</t>
+          <t>133639</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49210</t>
+          <t>46736</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77315</t>
+          <t>75589</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>153788</t>
+          <t>150438</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>199643</t>
+          <t>198387</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>127462</t>
+          <t>127862</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>166877</t>
+          <t>170269</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90709</t>
+          <t>91063</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>123646</t>
+          <t>125788</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>229933</t>
+          <t>228681</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>282170</t>
+          <t>280613</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19312</t>
+          <t>19659</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42004</t>
+          <t>41559</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26192</t>
+          <t>26144</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48818</t>
+          <t>48977</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50253</t>
+          <t>50355</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82046</t>
+          <t>83551</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64445</t>
+          <t>63973</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96374</t>
+          <t>96413</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39533</t>
+          <t>39880</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65599</t>
+          <t>66348</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109920</t>
+          <t>108314</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153830</t>
+          <t>152347</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53667</t>
+          <t>53375</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85236</t>
+          <t>85290</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50651</t>
+          <t>51602</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82562</t>
+          <t>80876</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113211</t>
+          <t>112408</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157193</t>
+          <t>156378</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69685</t>
+          <t>69372</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102848</t>
+          <t>103085</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45223</t>
+          <t>45832</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73971</t>
+          <t>73696</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122889</t>
+          <t>120941</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164483</t>
+          <t>164863</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92834</t>
+          <t>91905</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126740</t>
+          <t>127942</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>94499</t>
+          <t>96312</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>131800</t>
+          <t>129981</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>197578</t>
+          <t>197954</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>247565</t>
+          <t>247253</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,52%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13093</t>
+          <t>13406</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32047</t>
+          <t>32258</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28222</t>
+          <t>28380</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51487</t>
+          <t>52796</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47500</t>
+          <t>46373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78253</t>
+          <t>76927</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66641</t>
+          <t>67917</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101469</t>
+          <t>101484</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79594</t>
+          <t>79333</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>111728</t>
+          <t>113004</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155605</t>
+          <t>151472</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>204189</t>
+          <t>201420</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>93995</t>
+          <t>94777</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133368</t>
+          <t>132676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26132</t>
+          <t>26235</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47231</t>
+          <t>47371</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128538</t>
+          <t>128518</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172818</t>
+          <t>172470</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113358</t>
+          <t>112323</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152210</t>
+          <t>150567</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26807</t>
+          <t>26074</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50096</t>
+          <t>47520</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143643</t>
+          <t>148257</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>188486</t>
+          <t>192505</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>129771</t>
+          <t>127175</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>171234</t>
+          <t>168753</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39714</t>
+          <t>41484</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>64245</t>
+          <t>65592</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>177845</t>
+          <t>176897</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>226593</t>
+          <t>226577</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31446</t>
+          <t>31151</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56857</t>
+          <t>57971</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15898</t>
+          <t>16239</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37151</t>
+          <t>38444</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65289</t>
+          <t>68458</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>88680</t>
+          <t>89597</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>126415</t>
+          <t>126788</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25033</t>
+          <t>24964</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45637</t>
+          <t>44748</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121166</t>
+          <t>121871</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165087</t>
+          <t>165226</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>278640</t>
+          <t>281511</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>338757</t>
+          <t>342073</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>125820</t>
+          <t>128223</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>168727</t>
+          <t>170721</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>422333</t>
+          <t>417809</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>496972</t>
+          <t>492868</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>263934</t>
+          <t>264961</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>322237</t>
+          <t>322420</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>123012</t>
+          <t>124009</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>166436</t>
+          <t>166935</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>401466</t>
+          <t>400608</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>475710</t>
+          <t>475654</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>321059</t>
+          <t>319530</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>382807</t>
+          <t>382576</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>172657</t>
+          <t>173363</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>219011</t>
+          <t>221978</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>506386</t>
+          <t>505207</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>586532</t>
+          <t>584341</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48089</t>
+          <t>49301</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78700</t>
+          <t>79777</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44637</t>
+          <t>45242</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73702</t>
+          <t>75732</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>99765</t>
+          <t>101078</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>140109</t>
+          <t>143266</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>196973</t>
+          <t>196033</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>248992</t>
+          <t>252214</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>147693</t>
+          <t>143556</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>190508</t>
+          <t>189679</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>353672</t>
+          <t>356455</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>424818</t>
+          <t>431464</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>71598</t>
+          <t>74174</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>106031</t>
+          <t>106054</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>93150</t>
+          <t>94194</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>130911</t>
+          <t>131684</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>176873</t>
+          <t>177453</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>227785</t>
+          <t>228688</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>47963</t>
+          <t>49743</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>75694</t>
+          <t>79006</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>83823</t>
+          <t>83041</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>120630</t>
+          <t>120800</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>140243</t>
+          <t>142929</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>188310</t>
+          <t>190166</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>86595</t>
+          <t>86910</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>120892</t>
+          <t>122202</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>140504</t>
+          <t>141242</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>183876</t>
+          <t>185102</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>240736</t>
+          <t>239465</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>297397</t>
+          <t>293278</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>10391</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27440</t>
+          <t>26675</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>30195</t>
+          <t>29725</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>54766</t>
+          <t>54086</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>46086</t>
+          <t>43866</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>74305</t>
+          <t>72498</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>64638</t>
+          <t>64643</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>95761</t>
+          <t>94544</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>132621</t>
+          <t>131430</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>175348</t>
+          <t>173214</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>205567</t>
+          <t>202368</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>255056</t>
+          <t>256732</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>24776</t>
+          <t>24540</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>46117</t>
+          <t>46014</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>244233</t>
+          <t>240729</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>302396</t>
+          <t>297548</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>274113</t>
+          <t>278658</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>336968</t>
+          <t>338495</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>53282</t>
+          <t>52419</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>80895</t>
+          <t>80417</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>184181</t>
+          <t>187632</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>237658</t>
+          <t>240758</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>245361</t>
+          <t>248880</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>304879</t>
+          <t>305812</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>91199</t>
+          <t>91544</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>123459</t>
+          <t>122892</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>330916</t>
+          <t>327475</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>393587</t>
+          <t>391684</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>433481</t>
+          <t>431683</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>506153</t>
+          <t>503681</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>16768</t>
+          <t>16595</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>36152</t>
+          <t>35706</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>57566</t>
+          <t>57333</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>90448</t>
+          <t>88802</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>81048</t>
+          <t>79059</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>117212</t>
+          <t>116184</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>53010</t>
+          <t>54369</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>83642</t>
+          <t>81365</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>299493</t>
+          <t>303764</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>362434</t>
+          <t>365807</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>365694</t>
+          <t>366180</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>433056</t>
+          <t>431744</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,95%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>671356</t>
+          <t>671280</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>765749</t>
+          <t>763425</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>636057</t>
+          <t>633785</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>729572</t>
+          <t>727474</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1324550</t>
+          <t>1331987</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1460838</t>
+          <t>1463762</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>702449</t>
+          <t>698161</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>799019</t>
+          <t>794229</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>569083</t>
+          <t>568847</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>658274</t>
+          <t>662898</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4992,42 +4992,42 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
+          <t>19,66%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>1362601</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>1295896</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>1433426</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>20,52%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
           <t>19,52%</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>1362601</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>1292658</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>1425461</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>20,52%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>19,47%</t>
-        </is>
-      </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>916041</t>
+          <t>907865</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1025427</t>
+          <t>1013357</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>937575</t>
+          <t>940962</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1041900</t>
+          <t>1047418</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1890107</t>
+          <t>1885259</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2032780</t>
+          <t>2033157</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>169145</t>
+          <t>168887</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>221480</t>
+          <t>224807</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>225738</t>
+          <t>227874</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>287536</t>
+          <t>288406</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>413355</t>
+          <t>414053</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>492525</t>
+          <t>494988</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>595479</t>
+          <t>591696</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>687005</t>
+          <t>685591</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>783586</t>
+          <t>782916</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>884761</t>
+          <t>887044</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1401220</t>
+          <t>1406041</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1534528</t>
+          <t>1540589</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>138665</t>
+          <t>140250</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>180865</t>
+          <t>183784</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93050</t>
+          <t>93292</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>128504</t>
+          <t>128748</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>240200</t>
+          <t>244100</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>297851</t>
+          <t>297656</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,8%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88597</t>
+          <t>88225</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125472</t>
+          <t>123982</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48811</t>
+          <t>49582</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81932</t>
+          <t>81346</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>146606</t>
+          <t>148271</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>197180</t>
+          <t>196141</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64612</t>
+          <t>64539</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>98380</t>
+          <t>99388</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46751</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>77090</t>
+          <t>74152</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118951</t>
+          <t>119883</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>164585</t>
+          <t>164189</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18381</t>
+          <t>18734</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41094</t>
+          <t>40429</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16635</t>
+          <t>16754</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36117</t>
+          <t>35599</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41898</t>
+          <t>40335</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69086</t>
+          <t>67471</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48383</t>
+          <t>47736</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78393</t>
+          <t>78464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37232</t>
+          <t>37143</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64912</t>
+          <t>65164</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91647</t>
+          <t>91900</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>134682</t>
+          <t>134570</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144761</t>
+          <t>144675</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>187631</t>
+          <t>187073</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83900</t>
+          <t>86121</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120178</t>
+          <t>122970</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>241708</t>
+          <t>243010</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>298111</t>
+          <t>298643</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,56%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85470</t>
+          <t>85627</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>124002</t>
+          <t>122436</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50542</t>
+          <t>50060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79350</t>
+          <t>79621</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140361</t>
+          <t>141806</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>191253</t>
+          <t>191521</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64117</t>
+          <t>65097</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99630</t>
+          <t>99877</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52555</t>
+          <t>51438</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83897</t>
+          <t>83281</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>124585</t>
+          <t>124751</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>171955</t>
+          <t>170336</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19154</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20429</t>
+          <t>19842</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43335</t>
+          <t>43491</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28354</t>
+          <t>29186</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56327</t>
+          <t>55198</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43212</t>
+          <t>45313</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74277</t>
+          <t>76086</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59524</t>
+          <t>59454</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92580</t>
+          <t>92822</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111825</t>
+          <t>111396</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>155410</t>
+          <t>156591</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>230947</t>
+          <t>232567</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>281199</t>
+          <t>283632</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85122</t>
+          <t>86063</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118692</t>
+          <t>118326</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>331387</t>
+          <t>327420</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>390634</t>
+          <t>388452</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,77%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111368</t>
+          <t>111498</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>150542</t>
+          <t>152280</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30265</t>
+          <t>29001</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54958</t>
+          <t>53517</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>148939</t>
+          <t>149137</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>196759</t>
+          <t>194337</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>89861</t>
+          <t>89409</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>129060</t>
+          <t>128926</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34870</t>
+          <t>34727</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60188</t>
+          <t>60154</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>133218</t>
+          <t>130127</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>178153</t>
+          <t>177928</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15510</t>
+          <t>15089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37185</t>
+          <t>36989</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10632</t>
+          <t>10141</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27706</t>
+          <t>27976</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29236</t>
+          <t>29918</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55038</t>
+          <t>55757</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90151</t>
+          <t>89776</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127968</t>
+          <t>127659</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42074</t>
+          <t>40839</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69752</t>
+          <t>68347</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>136928</t>
+          <t>137683</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>185912</t>
+          <t>187510</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>448296</t>
+          <t>447472</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>516129</t>
+          <t>515353</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>252012</t>
+          <t>249364</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>306797</t>
+          <t>304351</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>716274</t>
+          <t>711045</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>800124</t>
+          <t>805462</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>216676</t>
+          <t>217634</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>275452</t>
+          <t>272912</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>124978</t>
+          <t>126841</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>168699</t>
+          <t>173057</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>354330</t>
+          <t>357748</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>428546</t>
+          <t>429532</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>152617</t>
+          <t>153611</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>202339</t>
+          <t>202754</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>110349</t>
+          <t>110144</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>156072</t>
+          <t>154372</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>277780</t>
+          <t>277520</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>344562</t>
+          <t>345757</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39018</t>
+          <t>38819</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>68947</t>
+          <t>69154</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35054</t>
+          <t>34958</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62140</t>
+          <t>63644</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>81039</t>
+          <t>79956</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>119809</t>
+          <t>121143</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>176627</t>
+          <t>180234</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>232554</t>
+          <t>235119</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>137019</t>
+          <t>137479</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>184360</t>
+          <t>185287</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>331195</t>
+          <t>328772</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>402584</t>
+          <t>400871</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>193628</t>
+          <t>190307</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>238409</t>
+          <t>235550</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>248092</t>
+          <t>246328</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>303935</t>
+          <t>302314</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>451536</t>
+          <t>452723</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>525716</t>
+          <t>523739</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>71831</t>
+          <t>72819</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>108214</t>
+          <t>108558</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>111817</t>
+          <t>112166</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>154083</t>
+          <t>154304</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>197268</t>
+          <t>196374</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>249483</t>
+          <t>251164</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>64320</t>
+          <t>66070</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>97930</t>
+          <t>98963</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>89089</t>
+          <t>89056</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>128366</t>
+          <t>127604</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>165401</t>
+          <t>165987</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>216308</t>
+          <t>217307</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>10816</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27923</t>
+          <t>27842</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>34531</t>
+          <t>35803</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>62555</t>
+          <t>64301</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>50522</t>
+          <t>51843</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>83991</t>
+          <t>83616</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>89494</t>
+          <t>90095</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>126937</t>
+          <t>127608</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>170541</t>
+          <t>171622</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>220666</t>
+          <t>219890</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>272643</t>
+          <t>274103</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>334726</t>
+          <t>336262</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>60393</t>
+          <t>60356</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>90477</t>
+          <t>90046</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>472186</t>
+          <t>474443</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>539563</t>
+          <t>537694</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>542376</t>
+          <t>538234</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>616174</t>
+          <t>614423</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>52026</t>
+          <t>51103</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>79966</t>
+          <t>81040</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>167697</t>
+          <t>167240</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>217240</t>
+          <t>216954</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>231087</t>
+          <t>230460</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>290311</t>
+          <t>284947</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>48211</t>
+          <t>49443</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>75897</t>
+          <t>76369</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>138747</t>
+          <t>139065</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>187957</t>
+          <t>186955</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>197294</t>
+          <t>197619</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>252200</t>
+          <t>255628</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>13973</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>30951</t>
+          <t>31083</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>45167</t>
+          <t>45798</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>76959</t>
+          <t>75459</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>65328</t>
+          <t>64842</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>98402</t>
+          <t>100378</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>34038</t>
+          <t>34502</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>58218</t>
+          <t>58804</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>164822</t>
+          <t>164245</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>214100</t>
+          <t>213502</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>204658</t>
+          <t>204964</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>262118</t>
+          <t>259383</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1295596</t>
+          <t>1290115</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1413568</t>
+          <t>1407336</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1323585</t>
+          <t>1310372</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1439552</t>
+          <t>1434678</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2635289</t>
+          <t>2640358</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2805073</t>
+          <t>2819560</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>689233</t>
+          <t>691980</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>785200</t>
+          <t>793788</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>596079</t>
+          <t>592716</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>688320</t>
+          <t>690393</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1311268</t>
+          <t>1309217</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1445791</t>
+          <t>1448520</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>543058</t>
+          <t>547221</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>635113</t>
+          <t>636411</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>529814</t>
+          <t>529061</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>617661</t>
+          <t>623278</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1104291</t>
+          <t>1097096</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1233359</t>
+          <t>1231177</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>130666</t>
+          <t>128427</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>178367</t>
+          <t>180815</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>199055</t>
+          <t>198125</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>260501</t>
+          <t>260393</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>341999</t>
+          <t>345230</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>420927</t>
+          <t>425953</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>541793</t>
+          <t>537274</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>631239</t>
+          <t>632204</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>671587</t>
+          <t>674600</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>775712</t>
+          <t>779280</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1245534</t>
+          <t>1233916</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1386471</t>
+          <t>1379367</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79922</t>
+          <t>82972</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117317</t>
+          <t>118351</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61230</t>
+          <t>61389</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93285</t>
+          <t>94212</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>152716</t>
+          <t>152282</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>201019</t>
+          <t>201732</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>133839</t>
+          <t>134174</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175395</t>
+          <t>176232</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83636</t>
+          <t>81445</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>114925</t>
+          <t>116788</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>226501</t>
+          <t>226888</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>280601</t>
+          <t>280132</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75739</t>
+          <t>74756</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>110154</t>
+          <t>110971</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>69132</t>
+          <t>68465</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99381</t>
+          <t>97909</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>152108</t>
+          <t>152568</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>200834</t>
+          <t>202627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16917</t>
+          <t>15762</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38072</t>
+          <t>37607</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>14717</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34190</t>
+          <t>34159</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35885</t>
+          <t>35863</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64502</t>
+          <t>63499</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43820</t>
+          <t>42613</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73028</t>
+          <t>72694</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48214</t>
+          <t>49261</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78498</t>
+          <t>79143</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101581</t>
+          <t>103190</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>145356</t>
+          <t>143385</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73940</t>
+          <t>73397</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>107265</t>
+          <t>108307</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54336</t>
+          <t>55037</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86770</t>
+          <t>86437</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137639</t>
+          <t>134539</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>186043</t>
+          <t>182776</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106654</t>
+          <t>105472</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>144930</t>
+          <t>142939</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111346</t>
+          <t>112170</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149093</t>
+          <t>148360</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>226989</t>
+          <t>230657</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>279741</t>
+          <t>281992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76727</t>
+          <t>77811</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>110762</t>
+          <t>111140</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67003</t>
+          <t>70500</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>101444</t>
+          <t>101325</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>155740</t>
+          <t>156190</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>202414</t>
+          <t>204105</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30406</t>
+          <t>30550</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33047</t>
+          <t>32275</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30137</t>
+          <t>30220</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55664</t>
+          <t>56696</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33232</t>
+          <t>34985</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61971</t>
+          <t>62200</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48878</t>
+          <t>51163</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79155</t>
+          <t>80775</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92005</t>
+          <t>91090</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129723</t>
+          <t>132567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109996</t>
+          <t>110169</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>150540</t>
+          <t>152217</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32008</t>
+          <t>30566</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56172</t>
+          <t>55484</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>152331</t>
+          <t>150283</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>196873</t>
+          <t>199218</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,03%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>138725</t>
+          <t>138338</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>182375</t>
+          <t>178301</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40005</t>
+          <t>38996</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63150</t>
+          <t>63914</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>184868</t>
+          <t>186642</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>233504</t>
+          <t>236882</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106457</t>
+          <t>107002</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>146582</t>
+          <t>146568</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21504</t>
+          <t>22112</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40430</t>
+          <t>41411</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>133834</t>
+          <t>133403</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>178966</t>
+          <t>178906</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22396</t>
+          <t>22305</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44705</t>
+          <t>44022</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22295</t>
+          <t>22959</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34147</t>
+          <t>34604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60471</t>
+          <t>62652</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58696</t>
+          <t>59422</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>92317</t>
+          <t>91167</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19188</t>
+          <t>19276</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39837</t>
+          <t>39963</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85153</t>
+          <t>85629</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>122851</t>
+          <t>122372</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>246223</t>
+          <t>250297</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>306557</t>
+          <t>307708</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>173023</t>
+          <t>172067</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>223800</t>
+          <t>218958</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>440443</t>
+          <t>442631</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>515316</t>
+          <t>514337</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>338613</t>
+          <t>338121</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>401636</t>
+          <t>402859</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>210465</t>
+          <t>216611</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>265664</t>
+          <t>266077</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>569997</t>
+          <t>570228</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>655350</t>
+          <t>652898</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>216181</t>
+          <t>213755</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>269815</t>
+          <t>270377</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>159599</t>
+          <t>160057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>206872</t>
+          <t>206382</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>381404</t>
+          <t>392044</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>457251</t>
+          <t>464271</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50488</t>
+          <t>50037</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84046</t>
+          <t>82634</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35907</t>
+          <t>37787</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63525</t>
+          <t>64007</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>95108</t>
+          <t>95092</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>137595</t>
+          <t>139788</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>163543</t>
+          <t>164804</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>214286</t>
+          <t>214287</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,7 +13261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>131683</t>
+          <t>132606</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>178452</t>
+          <t>175657</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>303619</t>
+          <t>307501</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>372661</t>
+          <t>375142</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>140368</t>
+          <t>139373</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>183890</t>
+          <t>182360</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>183331</t>
+          <t>181458</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>228733</t>
+          <t>229357</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>333204</t>
+          <t>335167</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>400251</t>
+          <t>400053</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>174136</t>
+          <t>174259</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>219751</t>
+          <t>223356</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>201715</t>
+          <t>202083</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>253071</t>
+          <t>251887</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>396567</t>
+          <t>395024</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>461539</t>
+          <t>464622</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>125446</t>
+          <t>122493</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>164530</t>
+          <t>165336</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>115925</t>
+          <t>115384</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>156971</t>
+          <t>156171</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>249927</t>
+          <t>250847</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>312519</t>
+          <t>310016</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>18946</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40561</t>
+          <t>40016</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>23665</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>48283</t>
+          <t>47230</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>48731</t>
+          <t>48699</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>79118</t>
+          <t>80551</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>71834</t>
+          <t>73846</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>106882</t>
+          <t>109076</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>113456</t>
+          <t>114530</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>157377</t>
+          <t>157353</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>196270</t>
+          <t>195752</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>251348</t>
+          <t>252228</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>55282</t>
+          <t>54085</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>83748</t>
+          <t>85646</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>215168</t>
+          <t>219546</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>273808</t>
+          <t>276303</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>280887</t>
+          <t>279621</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>346122</t>
+          <t>342398</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>75522</t>
+          <t>73678</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>106682</t>
+          <t>105606</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>280806</t>
+          <t>281698</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>344384</t>
+          <t>342742</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>366722</t>
+          <t>368928</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>437124</t>
+          <t>435239</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>59791</t>
+          <t>59987</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>90273</t>
+          <t>91747</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>156325</t>
+          <t>158180</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>205421</t>
+          <t>209292</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>226541</t>
+          <t>229950</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>287813</t>
+          <t>287456</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>8953</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>23693</t>
+          <t>24204</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>64631</t>
+          <t>62790</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>102116</t>
+          <t>101201</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>79521</t>
+          <t>78149</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>118030</t>
+          <t>117445</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>26783</t>
+          <t>27337</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>50553</t>
+          <t>49205</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>224888</t>
+          <t>225764</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>285451</t>
+          <t>285065</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>262858</t>
+          <t>264444</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>324975</t>
+          <t>326342</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>777457</t>
+          <t>779765</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>881102</t>
+          <t>879205</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>788596</t>
+          <t>786341</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>887608</t>
+          <t>890372</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1589890</t>
+          <t>1591227</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1734376</t>
+          <t>1740371</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1039944</t>
+          <t>1040301</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1153569</t>
+          <t>1152836</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1003241</t>
+          <t>1003028</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1116841</t>
+          <t>1114198</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2076422</t>
+          <t>2073174</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2234064</t>
+          <t>2229666</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>720423</t>
+          <t>722363</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>819388</t>
+          <t>818558</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>653236</t>
+          <t>656930</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>747264</t>
+          <t>752262</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1404579</t>
+          <t>1405575</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1536987</t>
+          <t>1540503</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>160481</t>
+          <t>162843</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>215280</t>
+          <t>214404</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>199846</t>
+          <t>196128</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>253816</t>
+          <t>258904</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>372014</t>
+          <t>373118</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>455577</t>
+          <t>454157</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>448291</t>
+          <t>451076</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>535143</t>
+          <t>529741</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>647864</t>
+          <t>650176</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>745338</t>
+          <t>747906</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1125806</t>
+          <t>1126867</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1258133</t>
+          <t>1255412</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
